--- a/Particle Counter/20260619/Particle_Counter_Data_June_19_2026_Flight.xlsx
+++ b/Particle Counter/20260619/Particle_Counter_Data_June_19_2026_Flight.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rtlines\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://webmailbyui-my.sharepoint.com/personal/kavin8137_byui_edu/Documents/Education/BYU-I/Research Project/NASA Aeronet/size_distribution_work/Particle Counter/20260619/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38F87236-9CA0-4D11-8CD5-8EB49F071413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{38F87236-9CA0-4D11-8CD5-8EB49F071413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C2094E5-FF7C-4896-A6E7-A4F68F2A9DB1}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="2820" windowWidth="21600" windowHeight="12645" xr2:uid="{499BC5DF-59C5-472F-B610-91F30912424B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{499BC5DF-59C5-472F-B610-91F30912424B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -471,13 +471,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62730979-826B-4FF9-A325-5468D6FD9001}">
-  <dimension ref="A1:T330"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V330"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="21" max="21" width="14.26953125" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,7 +541,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46192.62290509259</v>
       </c>
@@ -589,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46192.623599537037</v>
       </c>
@@ -639,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46192.624293981484</v>
       </c>
@@ -689,7 +691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46192.624988425923</v>
       </c>
@@ -739,7 +741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46192.62568287037</v>
       </c>
@@ -789,7 +791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46192.626377314817</v>
       </c>
@@ -839,7 +841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46192.627071759256</v>
       </c>
@@ -889,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46192.627766203703</v>
       </c>
@@ -939,7 +941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46192.628460648149</v>
       </c>
@@ -989,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46192.629155092596</v>
       </c>
@@ -1039,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46192.629849537036</v>
       </c>
@@ -1089,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46192.630543981482</v>
       </c>
@@ -1139,7 +1141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46192.631238425929</v>
       </c>
@@ -1189,7 +1191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46192.631932870368</v>
       </c>
@@ -1239,7 +1241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46192.632627314815</v>
       </c>
@@ -1289,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46192.633321759262</v>
       </c>
@@ -1339,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46192.634016203701</v>
       </c>
@@ -1389,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46192.634710648148</v>
       </c>
@@ -1439,7 +1441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46192.635405092595</v>
       </c>
@@ -1489,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46192.636099537034</v>
       </c>
@@ -1539,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46192.636793981481</v>
       </c>
@@ -1589,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46192.637488425928</v>
       </c>
@@ -1639,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>46192.638182870367</v>
       </c>
@@ -1689,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>46192.638877314814</v>
       </c>
@@ -1739,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>46192.63957175926</v>
       </c>
@@ -1789,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>46192.640266203707</v>
       </c>
@@ -1839,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>46192.640960648147</v>
       </c>
@@ -1889,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>46192.641655092593</v>
       </c>
@@ -1939,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>46192.64234953704</v>
       </c>
@@ -1989,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>46192.643043981479</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>46192.643738425926</v>
       </c>
@@ -2089,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>46192.644432870373</v>
       </c>
@@ -2139,7 +2141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>46192.645127314812</v>
       </c>
@@ -2189,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>46192.645821759259</v>
       </c>
@@ -2239,7 +2241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>46192.646516203706</v>
       </c>
@@ -2289,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>46192.647210648145</v>
       </c>
@@ -2339,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46192.647905092592</v>
       </c>
@@ -2389,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>46192.648599537039</v>
       </c>
@@ -2439,7 +2441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>46192.649293981478</v>
       </c>
@@ -2489,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>46192.649988425925</v>
       </c>
@@ -2539,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>46192.650682870371</v>
       </c>
@@ -2589,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>46192.651377314818</v>
       </c>
@@ -2639,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>46192.652071759258</v>
       </c>
@@ -2689,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>46192.652766203704</v>
       </c>
@@ -2739,7 +2741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46192.653460648151</v>
       </c>
@@ -2789,7 +2791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46192.65415509259</v>
       </c>
@@ -2839,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46192.654849537037</v>
       </c>
@@ -2889,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>46192.655543981484</v>
       </c>
@@ -2939,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>46192.656238425923</v>
       </c>
@@ -2989,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>46192.65693287037</v>
       </c>
@@ -3039,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>46192.657627314817</v>
       </c>
@@ -3089,7 +3091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>46192.658321759256</v>
       </c>
@@ -3139,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>46192.659016203703</v>
       </c>
@@ -3189,7 +3191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>46192.659710648149</v>
       </c>
@@ -3239,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>46192.660405092596</v>
       </c>
@@ -3289,7 +3291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>46192.661099537036</v>
       </c>
@@ -3339,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>46192.661793981482</v>
       </c>
@@ -3389,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>46192.662488425929</v>
       </c>
@@ -3439,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>46192.663182870368</v>
       </c>
@@ -3489,7 +3491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>46192.663877314815</v>
       </c>
@@ -3539,7 +3541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>46192.664571759262</v>
       </c>
@@ -3589,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>46192.665266203701</v>
       </c>
@@ -3639,7 +3641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>46192.665960648148</v>
       </c>
@@ -3689,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>46192.666655092595</v>
       </c>
@@ -3739,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>46192.667349537034</v>
       </c>
@@ -3789,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>46192.668043981481</v>
       </c>
@@ -3839,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>46192.668738425928</v>
       </c>
@@ -3888,8 +3890,10 @@
       <c r="T68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>46192.669432870367</v>
       </c>
@@ -3939,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>46192.670127314814</v>
       </c>
@@ -3989,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>46192.67082175926</v>
       </c>
@@ -4039,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>46192.671516203707</v>
       </c>
@@ -4088,8 +4092,10 @@
       <c r="T72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>46192.672210648147</v>
       </c>
@@ -4139,7 +4145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>46192.672905092593</v>
       </c>
@@ -4188,8 +4194,10 @@
       <c r="T74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U74" s="1"/>
+      <c r="V74" s="1"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>46192.67359953704</v>
       </c>
@@ -4239,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>46192.674293981479</v>
       </c>
@@ -4288,8 +4296,10 @@
       <c r="T76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>46192.674988425926</v>
       </c>
@@ -4339,7 +4349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>46192.675682870373</v>
       </c>
@@ -4389,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>46192.676377314812</v>
       </c>
@@ -4439,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>46192.677071759259</v>
       </c>
@@ -4488,8 +4498,10 @@
       <c r="T80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U80" s="1"/>
+      <c r="V80" s="1"/>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>46192.677766203706</v>
       </c>
@@ -4539,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>46192.678460648145</v>
       </c>
@@ -4588,8 +4600,10 @@
       <c r="T82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>46192.679155092592</v>
       </c>
@@ -4639,7 +4653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>46192.679849537039</v>
       </c>
@@ -4688,8 +4702,10 @@
       <c r="T84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U84" s="1"/>
+      <c r="V84" s="1"/>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>46192.680543981478</v>
       </c>
@@ -4739,7 +4755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>46192.681238425925</v>
       </c>
@@ -4788,8 +4804,10 @@
       <c r="T86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U86" s="1"/>
+      <c r="V86" s="1"/>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>46192.681932870371</v>
       </c>
@@ -4839,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>46192.682627314818</v>
       </c>
@@ -4888,8 +4906,10 @@
       <c r="T88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U88" s="1"/>
+      <c r="V88" s="1"/>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>46192.683321759258</v>
       </c>
@@ -4939,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>46192.684016203704</v>
       </c>
@@ -4988,8 +5008,10 @@
       <c r="T90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U90" s="1"/>
+      <c r="V90" s="1"/>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>46192.684710648151</v>
       </c>
@@ -5039,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>46192.68540509259</v>
       </c>
@@ -5088,8 +5110,10 @@
       <c r="T92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>46192.686099537037</v>
       </c>
@@ -5139,7 +5163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46192.686793981484</v>
       </c>
@@ -5189,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46192.687488425923</v>
       </c>
@@ -5239,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>46192.68818287037</v>
       </c>
@@ -5288,8 +5312,10 @@
       <c r="T96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U96" s="1"/>
+      <c r="V96" s="1"/>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>46192.688877314817</v>
       </c>
@@ -5339,7 +5365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>46192.689571759256</v>
       </c>
@@ -5388,8 +5414,10 @@
       <c r="T98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U98" s="1"/>
+      <c r="V98" s="1"/>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>46192.690266203703</v>
       </c>
@@ -5439,7 +5467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>46192.690960648149</v>
       </c>
@@ -5488,8 +5516,10 @@
       <c r="T100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>46192.691655092596</v>
       </c>
@@ -5539,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>46192.692349537036</v>
       </c>
@@ -5588,8 +5618,10 @@
       <c r="T102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U102" s="1"/>
+      <c r="V102" s="1"/>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>46192.693043981482</v>
       </c>
@@ -5639,7 +5671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>46192.693738425929</v>
       </c>
@@ -5688,8 +5720,10 @@
       <c r="T104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U104" s="1"/>
+      <c r="V104" s="1"/>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>46192.694432870368</v>
       </c>
@@ -5739,7 +5773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>46192.695127314815</v>
       </c>
@@ -5788,8 +5822,10 @@
       <c r="T106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>46192.695821759262</v>
       </c>
@@ -5839,7 +5875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>46192.696516203701</v>
       </c>
@@ -5888,8 +5924,10 @@
       <c r="T108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U108" s="1"/>
+      <c r="V108" s="1"/>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>46192.697210648148</v>
       </c>
@@ -5939,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>46192.697905092595</v>
       </c>
@@ -5988,8 +6026,10 @@
       <c r="T110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U110" s="1"/>
+      <c r="V110" s="1"/>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>46192.698599537034</v>
       </c>
@@ -6039,7 +6079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>46192.699293981481</v>
       </c>
@@ -6088,8 +6128,10 @@
       <c r="T112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U112" s="1"/>
+      <c r="V112" s="1"/>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>46192.699988425928</v>
       </c>
@@ -6139,7 +6181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>46192.700682870367</v>
       </c>
@@ -6188,8 +6230,10 @@
       <c r="T114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U114" s="1"/>
+      <c r="V114" s="1"/>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>46192.701377314814</v>
       </c>
@@ -6239,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>46192.70207175926</v>
       </c>
@@ -6288,8 +6332,10 @@
       <c r="T116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U116" s="1"/>
+      <c r="V116" s="1"/>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>46192.702766203707</v>
       </c>
@@ -6339,7 +6385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>46192.703460648147</v>
       </c>
@@ -6388,8 +6434,10 @@
       <c r="T118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U118" s="1"/>
+      <c r="V118" s="1"/>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>46192.704155092593</v>
       </c>
@@ -6439,7 +6487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>46192.70484953704</v>
       </c>
@@ -6488,8 +6536,10 @@
       <c r="T120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U120" s="1"/>
+      <c r="V120" s="1"/>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>46192.705543981479</v>
       </c>
@@ -6539,7 +6589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>46192.706238425926</v>
       </c>
@@ -6588,8 +6638,10 @@
       <c r="T122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U122" s="1"/>
+      <c r="V122" s="1"/>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>46192.706932870373</v>
       </c>
@@ -6639,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>46192.707627314812</v>
       </c>
@@ -6688,8 +6740,10 @@
       <c r="T124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U124" s="1"/>
+      <c r="V124" s="1"/>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>46192.708321759259</v>
       </c>
@@ -6739,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>46192.709016203706</v>
       </c>
@@ -6788,8 +6842,10 @@
       <c r="T126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U126" s="1"/>
+      <c r="V126" s="1"/>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>46192.709710648145</v>
       </c>
@@ -6838,8 +6894,10 @@
       <c r="T127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U127" s="1"/>
+      <c r="V127" s="1"/>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>46192.710405092592</v>
       </c>
@@ -6888,8 +6946,10 @@
       <c r="T128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U128" s="1"/>
+      <c r="V128" s="1"/>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>46192.711099537039</v>
       </c>
@@ -6938,8 +6998,10 @@
       <c r="T129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>46192.711793981478</v>
       </c>
@@ -6988,8 +7050,10 @@
       <c r="T130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U130" s="1"/>
+      <c r="V130" s="1"/>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>46192.712488425925</v>
       </c>
@@ -7038,8 +7102,10 @@
       <c r="T131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U131" s="1"/>
+      <c r="V131" s="1"/>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>46192.713182870371</v>
       </c>
@@ -7088,8 +7154,10 @@
       <c r="T132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U132" s="1"/>
+      <c r="V132" s="1"/>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>46192.713877314818</v>
       </c>
@@ -7138,8 +7206,10 @@
       <c r="T133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U133" s="1"/>
+      <c r="V133" s="1"/>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>46192.714571759258</v>
       </c>
@@ -7188,8 +7258,10 @@
       <c r="T134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U134" s="1"/>
+      <c r="V134" s="1"/>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>46192.715266203704</v>
       </c>
@@ -7238,8 +7310,10 @@
       <c r="T135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U135" s="1"/>
+      <c r="V135" s="1"/>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>46192.715960648151</v>
       </c>
@@ -7288,8 +7362,10 @@
       <c r="T136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U136" s="1"/>
+      <c r="V136" s="1"/>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>46192.71665509259</v>
       </c>
@@ -7338,8 +7414,10 @@
       <c r="T137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U137" s="1"/>
+      <c r="V137" s="1"/>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>46192.717349537037</v>
       </c>
@@ -7388,8 +7466,10 @@
       <c r="T138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U138" s="1"/>
+      <c r="V138" s="1"/>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>46192.718043981484</v>
       </c>
@@ -7438,8 +7518,10 @@
       <c r="T139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U139" s="1"/>
+      <c r="V139" s="1"/>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>46192.718738425923</v>
       </c>
@@ -7488,8 +7570,10 @@
       <c r="T140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U140" s="1"/>
+      <c r="V140" s="1"/>
+    </row>
+    <row r="141" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>46192.71943287037</v>
       </c>
@@ -7538,8 +7622,10 @@
       <c r="T141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U141" s="1"/>
+      <c r="V141" s="1"/>
+    </row>
+    <row r="142" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>46192.720127314817</v>
       </c>
@@ -7588,8 +7674,10 @@
       <c r="T142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U142" s="1"/>
+      <c r="V142" s="1"/>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>46192.720821759256</v>
       </c>
@@ -7638,8 +7726,10 @@
       <c r="T143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U143" s="1"/>
+      <c r="V143" s="1"/>
+    </row>
+    <row r="144" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>46192.721516203703</v>
       </c>
@@ -7688,8 +7778,10 @@
       <c r="T144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U144" s="1"/>
+      <c r="V144" s="1"/>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>46192.722210648149</v>
       </c>
@@ -7738,8 +7830,10 @@
       <c r="T145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U145" s="1"/>
+      <c r="V145" s="1"/>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>46192.722905092596</v>
       </c>
@@ -7788,8 +7882,10 @@
       <c r="T146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U146" s="1"/>
+      <c r="V146" s="1"/>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>46192.723599537036</v>
       </c>
@@ -7838,8 +7934,10 @@
       <c r="T147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U147" s="1"/>
+      <c r="V147" s="1"/>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>46192.724293981482</v>
       </c>
@@ -7888,8 +7986,10 @@
       <c r="T148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U148" s="1"/>
+      <c r="V148" s="1"/>
+    </row>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>46192.724988425929</v>
       </c>
@@ -7938,8 +8038,10 @@
       <c r="T149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U149" s="1"/>
+      <c r="V149" s="1"/>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>46192.725682870368</v>
       </c>
@@ -7988,8 +8090,10 @@
       <c r="T150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U150" s="1"/>
+      <c r="V150" s="1"/>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>46192.726377314815</v>
       </c>
@@ -8038,8 +8142,10 @@
       <c r="T151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U151" s="1"/>
+      <c r="V151" s="1"/>
+    </row>
+    <row r="152" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>46192.727071759262</v>
       </c>
@@ -8088,8 +8194,10 @@
       <c r="T152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U152" s="1"/>
+      <c r="V152" s="1"/>
+    </row>
+    <row r="153" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>46192.727766203701</v>
       </c>
@@ -8138,8 +8246,10 @@
       <c r="T153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U153" s="1"/>
+      <c r="V153" s="1"/>
+    </row>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>46192.728460648148</v>
       </c>
@@ -8188,8 +8298,10 @@
       <c r="T154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U154" s="1"/>
+      <c r="V154" s="1"/>
+    </row>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>46192.729155092595</v>
       </c>
@@ -8238,8 +8350,10 @@
       <c r="T155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U155" s="1"/>
+      <c r="V155" s="1"/>
+    </row>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>46192.729849537034</v>
       </c>
@@ -8288,8 +8402,10 @@
       <c r="T156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U156" s="1"/>
+      <c r="V156" s="1"/>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>46192.730543981481</v>
       </c>
@@ -8338,8 +8454,10 @@
       <c r="T157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U157" s="1"/>
+      <c r="V157" s="1"/>
+    </row>
+    <row r="158" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>46192.731238425928</v>
       </c>
@@ -8388,8 +8506,10 @@
       <c r="T158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U158" s="1"/>
+      <c r="V158" s="1"/>
+    </row>
+    <row r="159" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>46192.731932870367</v>
       </c>
@@ -8438,8 +8558,10 @@
       <c r="T159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U159" s="1"/>
+      <c r="V159" s="1"/>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>46192.732627314814</v>
       </c>
@@ -8488,8 +8610,10 @@
       <c r="T160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U160" s="1"/>
+      <c r="V160" s="1"/>
+    </row>
+    <row r="161" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>46192.73332175926</v>
       </c>
@@ -8538,8 +8662,10 @@
       <c r="T161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U161" s="1"/>
+      <c r="V161" s="1"/>
+    </row>
+    <row r="162" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>46192.734016203707</v>
       </c>
@@ -8588,8 +8714,10 @@
       <c r="T162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U162" s="1"/>
+      <c r="V162" s="1"/>
+    </row>
+    <row r="163" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>46192.734710648147</v>
       </c>
@@ -8638,8 +8766,10 @@
       <c r="T163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U163" s="1"/>
+      <c r="V163" s="1"/>
+    </row>
+    <row r="164" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>46192.735405092593</v>
       </c>
@@ -8688,8 +8818,10 @@
       <c r="T164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U164" s="1"/>
+      <c r="V164" s="1"/>
+    </row>
+    <row r="165" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>46192.73609953704</v>
       </c>
@@ -8738,8 +8870,10 @@
       <c r="T165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U165" s="1"/>
+      <c r="V165" s="1"/>
+    </row>
+    <row r="166" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>46192.736793981479</v>
       </c>
@@ -8788,8 +8922,10 @@
       <c r="T166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U166" s="1"/>
+      <c r="V166" s="1"/>
+    </row>
+    <row r="167" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>46192.737488425926</v>
       </c>
@@ -8838,8 +8974,10 @@
       <c r="T167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U167" s="1"/>
+      <c r="V167" s="1"/>
+    </row>
+    <row r="168" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>46192.738182870373</v>
       </c>
@@ -8889,7 +9027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>46192.738877314812</v>
       </c>
@@ -8939,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>46192.739571759259</v>
       </c>
@@ -8989,7 +9127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>46192.740266203706</v>
       </c>
@@ -9039,7 +9177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>46192.740960648145</v>
       </c>
@@ -9089,7 +9227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>46192.741655092592</v>
       </c>
@@ -9139,7 +9277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>46192.742349537039</v>
       </c>
@@ -9189,7 +9327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>46192.743043981478</v>
       </c>
@@ -9239,7 +9377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>46192.743738425925</v>
       </c>
@@ -9289,7 +9427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>46192.744432870371</v>
       </c>
@@ -9339,7 +9477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>46192.745127314818</v>
       </c>
@@ -9389,7 +9527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>46192.745821759258</v>
       </c>
@@ -9439,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>46192.746516203704</v>
       </c>
@@ -9489,7 +9627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>46192.747210648151</v>
       </c>
@@ -9539,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>46192.74790509259</v>
       </c>
@@ -9589,7 +9727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>46192.748599537037</v>
       </c>
@@ -9639,7 +9777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>46192.749293981484</v>
       </c>
@@ -9689,7 +9827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>46192.749988425923</v>
       </c>
@@ -9739,7 +9877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>46192.75068287037</v>
       </c>
@@ -9789,7 +9927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>46192.751377314817</v>
       </c>
@@ -9839,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>46192.752071759256</v>
       </c>
@@ -9889,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>46192.752766203703</v>
       </c>
@@ -9939,7 +10077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>46192.753460648149</v>
       </c>
@@ -9989,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>46192.754155092596</v>
       </c>
@@ -10039,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>46192.754849537036</v>
       </c>
@@ -10089,7 +10227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>46192.755543981482</v>
       </c>
@@ -10139,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>46192.756238425929</v>
       </c>
@@ -10189,7 +10327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>46192.756932870368</v>
       </c>
@@ -10239,7 +10377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>46192.757627314815</v>
       </c>
@@ -10289,7 +10427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>46192.758321759262</v>
       </c>
@@ -10339,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>46192.759016203701</v>
       </c>
@@ -10389,7 +10527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>46192.759710648148</v>
       </c>
@@ -10439,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>46192.760405092595</v>
       </c>
@@ -10489,7 +10627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>46192.761099537034</v>
       </c>
@@ -10539,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>46192.761793981481</v>
       </c>
@@ -10589,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>46192.762488425928</v>
       </c>
@@ -10639,7 +10777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>46192.763182870367</v>
       </c>
@@ -10689,7 +10827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>46192.763877314814</v>
       </c>
@@ -10739,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>46192.76457175926</v>
       </c>
@@ -10789,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>46192.765266203707</v>
       </c>
@@ -10839,7 +10977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>46192.765960648147</v>
       </c>
@@ -10889,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>46192.766655092593</v>
       </c>
@@ -10939,7 +11077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>46192.76734953704</v>
       </c>
@@ -10989,7 +11127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>46192.768043981479</v>
       </c>
@@ -11039,7 +11177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>46192.768738425926</v>
       </c>
@@ -11089,7 +11227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>46192.769432870373</v>
       </c>
@@ -11139,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>46192.770127314812</v>
       </c>
@@ -11189,7 +11327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>46192.770821759259</v>
       </c>
@@ -11239,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>46192.771516203706</v>
       </c>
@@ -11289,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>46192.772210648145</v>
       </c>
@@ -11339,7 +11477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>46192.772905092592</v>
       </c>
@@ -11389,7 +11527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>46192.773599537039</v>
       </c>
@@ -11439,7 +11577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>46192.774293981478</v>
       </c>
@@ -11489,7 +11627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>46192.774988425925</v>
       </c>
@@ -11539,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>46192.775682870371</v>
       </c>
@@ -11589,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>46192.776377314818</v>
       </c>
@@ -11639,7 +11777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>46192.777071759258</v>
       </c>
@@ -11689,7 +11827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>46192.777766203704</v>
       </c>
@@ -11739,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>46192.778460648151</v>
       </c>
@@ -11789,7 +11927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>46192.77915509259</v>
       </c>
@@ -11839,7 +11977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>46192.779849537037</v>
       </c>
@@ -11889,7 +12027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>46192.780543981484</v>
       </c>
@@ -11939,7 +12077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>46192.781238425923</v>
       </c>
@@ -11989,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>46192.78193287037</v>
       </c>
@@ -12039,7 +12177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>46192.782627314817</v>
       </c>
@@ -12089,7 +12227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>46192.783321759256</v>
       </c>
@@ -12139,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>46192.784016203703</v>
       </c>
@@ -12189,7 +12327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>46192.784710648149</v>
       </c>
@@ -12239,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>46192.785405092596</v>
       </c>
@@ -12289,7 +12427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>46192.786099537036</v>
       </c>
@@ -12339,7 +12477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>46192.786793981482</v>
       </c>
@@ -12389,7 +12527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>46192.787488425929</v>
       </c>
@@ -12439,7 +12577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>46192.788182870368</v>
       </c>
@@ -12489,7 +12627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>46192.788877314815</v>
       </c>
@@ -12539,7 +12677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>46192.789571759262</v>
       </c>
@@ -12589,7 +12727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>46192.790266203701</v>
       </c>
@@ -12639,7 +12777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>46192.790960648148</v>
       </c>
@@ -12689,7 +12827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>46192.791655092595</v>
       </c>
@@ -12739,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>46192.792349537034</v>
       </c>
@@ -12789,7 +12927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>46192.793043981481</v>
       </c>
@@ -12839,7 +12977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>46192.793738425928</v>
       </c>
@@ -12889,7 +13027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>46192.794432870367</v>
       </c>
@@ -12939,7 +13077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>46192.795127314814</v>
       </c>
@@ -12989,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>46192.79582175926</v>
       </c>
@@ -13039,7 +13177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>46192.796516203707</v>
       </c>
@@ -13089,7 +13227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>46192.797210648147</v>
       </c>
@@ -13139,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>46192.797905092593</v>
       </c>
@@ -13189,7 +13327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>46192.79859953704</v>
       </c>
@@ -13239,7 +13377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>46192.799293981479</v>
       </c>
@@ -13289,7 +13427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>46192.799988425926</v>
       </c>
@@ -13339,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>46192.800682870373</v>
       </c>
@@ -13389,7 +13527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>46192.801377314812</v>
       </c>
@@ -13439,7 +13577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>46192.802071759259</v>
       </c>
@@ -13489,7 +13627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>46192.802766203706</v>
       </c>
@@ -13539,7 +13677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>46192.803460648145</v>
       </c>
@@ -13589,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>46192.804155092592</v>
       </c>
@@ -13639,7 +13777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>46192.804849537039</v>
       </c>
@@ -13689,7 +13827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>46192.805543981478</v>
       </c>
@@ -13739,7 +13877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>46192.806238425925</v>
       </c>
@@ -13789,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>46192.806932870371</v>
       </c>
@@ -13839,7 +13977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>46192.807627314818</v>
       </c>
@@ -13889,7 +14027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>46192.808321759258</v>
       </c>
@@ -13939,7 +14077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>46192.809016203704</v>
       </c>
@@ -13989,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>46192.809710648151</v>
       </c>
@@ -14039,7 +14177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>46192.81040509259</v>
       </c>
@@ -14089,7 +14227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>46192.811099537037</v>
       </c>
@@ -14139,7 +14277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>46192.811793981484</v>
       </c>
@@ -14189,7 +14327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>46192.812488425923</v>
       </c>
@@ -14239,7 +14377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>46192.81318287037</v>
       </c>
@@ -14289,7 +14427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>46192.813877314817</v>
       </c>
@@ -14339,7 +14477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>46192.814571759256</v>
       </c>
@@ -14389,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>46192.815266203703</v>
       </c>
@@ -14439,7 +14577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>46192.815960648149</v>
       </c>
@@ -14489,7 +14627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>46192.816655092596</v>
       </c>
@@ -14539,7 +14677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>46192.817349537036</v>
       </c>
@@ -14589,7 +14727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>46192.818043981482</v>
       </c>
@@ -14639,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>46192.818738425929</v>
       </c>
@@ -14689,7 +14827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>46192.819432870368</v>
       </c>
@@ -14739,7 +14877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>46192.820127314815</v>
       </c>
@@ -14789,7 +14927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>46192.820821759262</v>
       </c>
@@ -14839,7 +14977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>46192.821516203701</v>
       </c>
@@ -14889,7 +15027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>46192.822210648148</v>
       </c>
@@ -14939,7 +15077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>46192.822905092595</v>
       </c>
@@ -14989,7 +15127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>46192.823599537034</v>
       </c>
@@ -15039,7 +15177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>46192.824293981481</v>
       </c>
@@ -15089,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>46192.824988425928</v>
       </c>
@@ -15139,7 +15277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>46192.825682870367</v>
       </c>
@@ -15189,7 +15327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>46192.826377314814</v>
       </c>
@@ -15239,7 +15377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>46192.82707175926</v>
       </c>
@@ -15289,7 +15427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>46192.827766203707</v>
       </c>
@@ -15339,7 +15477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>46192.828460648147</v>
       </c>
@@ -15389,7 +15527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>46192.829155092593</v>
       </c>
@@ -15439,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>46192.82984953704</v>
       </c>
@@ -15489,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>46192.830543981479</v>
       </c>
@@ -15539,7 +15677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>46192.831238425926</v>
       </c>
@@ -15589,7 +15727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>46192.831932870373</v>
       </c>
@@ -15639,7 +15777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>46192.832627314812</v>
       </c>
@@ -15689,7 +15827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>46192.833321759259</v>
       </c>
@@ -15739,7 +15877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>46192.834016203706</v>
       </c>
@@ -15789,7 +15927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>46192.834710648145</v>
       </c>
@@ -15839,7 +15977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>46192.835405092592</v>
       </c>
@@ -15889,7 +16027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>46192.836099537039</v>
       </c>
@@ -15939,7 +16077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>46192.836793981478</v>
       </c>
@@ -15989,7 +16127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>46192.837488425925</v>
       </c>
@@ -16039,7 +16177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>46192.838182870371</v>
       </c>
@@ -16089,7 +16227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>46192.838877314818</v>
       </c>
@@ -16139,7 +16277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>46192.839571759258</v>
       </c>
@@ -16189,7 +16327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>46192.840266203704</v>
       </c>
@@ -16239,7 +16377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>46192.840960648151</v>
       </c>
@@ -16289,7 +16427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>46192.84165509259</v>
       </c>
@@ -16339,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>46192.842349537037</v>
       </c>
@@ -16389,7 +16527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>46192.843043981484</v>
       </c>
@@ -16439,7 +16577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>46192.843738425923</v>
       </c>
@@ -16489,7 +16627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>46192.84443287037</v>
       </c>
@@ -16539,7 +16677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>46192.845127314817</v>
       </c>
@@ -16589,7 +16727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>46192.845821759256</v>
       </c>
@@ -16639,7 +16777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>46192.846516203703</v>
       </c>
@@ -16689,7 +16827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>46192.847210648149</v>
       </c>
@@ -16739,7 +16877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>46192.847905092596</v>
       </c>
@@ -16789,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>46192.848599537036</v>
       </c>
@@ -16839,7 +16977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>46192.849293981482</v>
       </c>
@@ -16889,7 +17027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>46192.849988425929</v>
       </c>
@@ -16939,7 +17077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>46192.850682870368</v>
       </c>
